--- a/alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx
+++ b/alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx
@@ -6144,7 +6144,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6249,7 +6249,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6336,7 +6336,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6413,7 +6413,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6577,7 +6577,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6833,7 +6833,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6954,7 +6954,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7075,7 +7075,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7196,7 +7196,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7317,7 +7317,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -39861,7 +39861,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx
+++ b/alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx
@@ -7979,7 +7979,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -7998,6 +7998,117 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E38 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同值（建置時檢查）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">f_hbm_ref</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對照：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Broadcom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代購比例</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">avgo/dist/20261025_Broadcom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
@@ -8017,30 +8128,244 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E38 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同值（建置時檢查）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">f_hbm_ref</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">對照：</t>
+      <t xml:space="preserve">In!E58</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">世芯不沿用（見下列）；只作 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高值</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">f_al</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">世芯代購 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">並計入營收的比例</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美系外資：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trainium 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生命週期可服務市場「不含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」（旺得富 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interested-party</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18–25% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍高於代購 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情形</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司未揭露 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">由誰採購：未找到；高值＝</t>
     </r>
     <r>
       <rPr>
@@ -8059,7 +8384,50 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">模型的 </t>
+      <t xml:space="preserve">模型 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，只放 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">m_hbm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代購 </t>
     </r>
     <r>
       <rPr>
@@ -8078,7 +8446,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">代購比例</t>
+      <t xml:space="preserve">的毛利率（只在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">f_al &gt; 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時有作用）</t>
     </r>
   </si>
   <si>
@@ -8128,244 +8515,18 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E58</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">世芯不沿用（見下列）；只作 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高值</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">f_al</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">世芯代購 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">並計入營收的比例</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美系外資：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Trainium 4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">生命週期可服務市場「不含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」（旺得富 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-08-17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Interested-party</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18–25% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仍高於代購 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情形</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司未揭露 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">由誰採購：未找到；高值＝</t>
+      <t xml:space="preserve">In!E59</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">沿用 </t>
     </r>
     <r>
       <rPr>
@@ -8384,119 +8545,100 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，只放 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">m_hbm</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">代購 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的毛利率（只在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">f_al &gt; 0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時有作用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">avgo/dist/20261025_Broadcom</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">模型</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mv_trn_26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Marvell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWS Trainium </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（份額加總檢查用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邁威爾模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8515,41 +8657,8 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E59</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">沿用 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Broadcom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mv_trn_26</t>
+      <t xml:space="preserve">In!E45</t>
+    </r>
   </si>
   <si>
     <r>
@@ -8569,6 +8678,68 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">模型；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Marvell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（基準）＋世芯（高）≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（建置時檢查）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mv_trn_27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Marvell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">占 </t>
     </r>
     <r>
@@ -8598,7 +8769,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CY2026</t>
+      <t xml:space="preserve">CY2027</t>
     </r>
     <r>
       <rPr>
@@ -8619,7 +8790,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -8638,7 +8809,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8657,8 +8828,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E45</t>
-    </r>
+      <t xml:space="preserve">In!E46</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mv_trn_28</t>
   </si>
   <si>
     <r>
@@ -8678,68 +8852,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">模型；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Marvell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（基準）＋世芯（高）≤ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（建置時檢查）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mv_trn_27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Marvell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">占 </t>
     </r>
     <r>
@@ -8769,7 +8881,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CY2027</t>
+      <t xml:space="preserve">CY2028</t>
     </r>
     <r>
       <rPr>
@@ -8790,7 +8902,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -8809,119 +8921,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!E46</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mv_trn_28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Marvell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">占 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AWS Trainium </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2028</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（份額加總檢查用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邁威爾模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -39918,7 +39918,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -39937,7 +39937,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx
+++ b/alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx
@@ -6125,26 +6125,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6230,26 +6230,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6317,26 +6317,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6394,26 +6394,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6558,26 +6558,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6814,26 +6814,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6935,26 +6935,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7056,26 +7056,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7177,26 +7177,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7298,26 +7298,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -39842,26 +39842,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
